--- a/April Roster.xlsx
+++ b/April Roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MNABIL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moody\Downloads\whatsapp-bot - EN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B06CF50F-CA40-4381-A2AD-774D27FD41A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0522DEC8-A0A7-4636-977D-7806D4508506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="61440" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EID" sheetId="8" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1405,15 +1402,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="26">
         <v>3</v>
       </c>
       <c r="B5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
+      <c r="C5" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>10</v>
@@ -1488,8 +1485,8 @@
       <c r="B7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
+      <c r="C7" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>14</v>
@@ -1957,43 +1954,43 @@
         <v>14</v>
       </c>
       <c r="C20" s="3">
-        <f>COUNTIF(C3:C19,"M")</f>
+        <f t="shared" ref="C20:L20" si="0">COUNTIF(C3:C19,"M")</f>
+        <v>3</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D20" s="3">
-        <f>COUNTIF(D3:D19,"M")</f>
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <f>COUNTIF(E3:E19,"M")</f>
+      <c r="F20" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F20" s="3">
-        <f>COUNTIF(F3:F19,"M")</f>
-        <v>8</v>
-      </c>
-      <c r="G20" s="3">
-        <f>COUNTIF(G3:G19,"M")</f>
+      <c r="H20" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H20" s="3">
-        <f>COUNTIF(H3:H19,"M")</f>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I20" s="3">
-        <f>COUNTIF(I3:I19,"M")</f>
-        <v>5</v>
-      </c>
       <c r="J20" s="3">
-        <f>COUNTIF(J3:J19,"M")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="K20" s="3">
-        <f>COUNTIF(K3:K19,"M")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="L20" s="3">
-        <f>COUNTIF(L3:L19,"M")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -2003,43 +2000,43 @@
         <v>9</v>
       </c>
       <c r="C21" s="32">
-        <f>COUNTIF(C4:C19,"B")</f>
+        <f t="shared" ref="C21:L21" si="1">COUNTIF(C4:C19,"B")</f>
         <v>0</v>
       </c>
       <c r="D21" s="32">
-        <f>COUNTIF(D4:D19,"B")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E21" s="32">
-        <f>COUNTIF(E4:E19,"B")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F21" s="32">
-        <f>COUNTIF(F4:F19,"B")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G21" s="32">
-        <f>COUNTIF(G4:G19,"B")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H21" s="32">
-        <f>COUNTIF(H4:H19,"B")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I21" s="32">
-        <f>COUNTIF(I4:I19,"B")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J21" s="32">
-        <f>COUNTIF(J4:J19,"B")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K21" s="32">
-        <f>COUNTIF(K4:K19,"B")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L21" s="32">
-        <f>COUNTIF(L4:L19,"B")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2049,43 +2046,43 @@
         <v>12</v>
       </c>
       <c r="C22" s="27">
-        <f>COUNTIF(C3:C19,"E")</f>
+        <f t="shared" ref="C22:L22" si="2">COUNTIF(C3:C19,"E")</f>
         <v>2</v>
       </c>
       <c r="D22" s="27">
-        <f>COUNTIF(D3:D19,"E")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E22" s="27">
-        <f>COUNTIF(E3:E19,"E")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F22" s="27">
-        <f>COUNTIF(F3:F19,"E")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G22" s="27">
-        <f>COUNTIF(G3:G19,"E")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H22" s="27">
-        <f>COUNTIF(H3:H19,"E")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I22" s="27">
-        <f>COUNTIF(I3:I19,"E")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J22" s="27">
-        <f>COUNTIF(J3:J19,"E")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K22" s="27">
-        <f>COUNTIF(K3:K19,"E")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L22" s="27">
-        <f>COUNTIF(L3:L19,"E")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2095,43 +2092,43 @@
         <v>17</v>
       </c>
       <c r="C23" s="36">
-        <f>COUNTIF(C3:C19,"N")</f>
+        <f t="shared" ref="C23:L23" si="3">COUNTIF(C3:C19,"N")</f>
         <v>1</v>
       </c>
       <c r="D23" s="36">
-        <f>COUNTIF(D3:D19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E23" s="36">
-        <f>COUNTIF(E3:E19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F23" s="36">
-        <f>COUNTIF(F3:F19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G23" s="36">
-        <f>COUNTIF(G3:G19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H23" s="36">
-        <f>COUNTIF(H3:H19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I23" s="36">
-        <f>COUNTIF(I3:I19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J23" s="36">
-        <f>COUNTIF(J3:J19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K23" s="36">
-        <f>COUNTIF(K3:K19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L23" s="36">
-        <f>COUNTIF(L3:L19,"N")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>

--- a/April Roster.xlsx
+++ b/April Roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moody\Downloads\whatsapp-bot - EN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0522DEC8-A0A7-4636-977D-7806D4508506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12362DC-DE16-4258-AF9F-D38E78A8A183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="61440" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1402,15 +1402,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>3</v>
       </c>
       <c r="B5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>43</v>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>10</v>
@@ -1485,8 +1485,8 @@
       <c r="B7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>43</v>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>14</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C20" s="3">
         <f t="shared" ref="C20:L20" si="0">COUNTIF(C3:C19,"M")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="3">
         <f t="shared" si="0"/>
